--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_08_RAG Pipeline _ Retrieval Evaluation/Day_08_Phan_01_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_08_RAG Pipeline _ Retrieval Evaluation/Day_08_Phan_01_19_Cau.xlsx
@@ -1167,7 +1167,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1176,7 +1176,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt phần có thể chạy song song với kết luận phụ thuộc chúng.</t>
+          <t>Khi phân rã và kết hợp lại câu hỏi so sánh hai phiên bản chính sách ở hai nguồn riêng: (a) Tạo sub-query lấy điều kiện và hạn chót năm 2026; (b) Tạo sub-query lấy hạn chót năm 2025; (c) Giữ dấu vết nguồn riêng cho từng phiên bản tài liệu; (d) Chỉ đưa ra kết luận so sánh sau khi đã thu thập đủ hạn chót của cả hai năm. Tuyệt đối không dùng trí nhớ của mô hình để suy diễn khi thiếu dữ liệu.</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o3 → o2 → o4 → o5 → o1</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt bước xây dựng index offline với bước tìm kiếm khi nhận query.</t>
+          <t>Quy trình triển khai tìm kiếm từ khóa (lexical search BM25) đúng trình tự nhân quả: 1. Xây dựng chỉ mục BM25 từ các token trong kho tài liệu ở pha offline (o3) -&gt; 2. Khi nhận truy vấn, tokenize query theo cùng quy ước chuẩn hóa (o2) -&gt; 3. Chấm điểm truy vấn trên chỉ mục BM25 (o4) -&gt; 4. Sắp xếp điểm giảm dần và giới hạn ở top-k kết quả (o5) -&gt; 5. Trả top-k bản ghi kèm mã định danh và metadata (o1).</t>
         </is>
       </c>
     </row>
